--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260814.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260814.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.71%</t>
+          <t>9.59%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.21%</t>
+          <t>9.27%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>371,139,486</t>
+          <t>39,027,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>6.17%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>39,027,000</t>
+          <t>371,139,486</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.82%</t>
+          <t>5.98%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>188,260,000</t>
+          <t>608,249,270</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.65%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>608,249,270</t>
+          <t>188,260,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,056</t>
+          <t>2,114</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -836,183 +836,183 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>64,840,000</t>
+          <t>366,839,964</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>132,969,945</t>
+          <t>64,840,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>366,839,964</t>
+          <t>132,969,945</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>26,367,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>26,367,000</t>
+          <t>83,490,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>83,490,000</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>98,854,442</t>
+          <t>230,616,516</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>98,854,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -1056,73 +1056,73 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>131,978,000</t>
+          <t>29,028,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>35,720,000</t>
+          <t>131,978,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>29,028,000</t>
+          <t>35,720,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>259,999,845</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>259,999,845</t>
+          <t>273,066,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,884,082,647</t>
+          <t>14,437,150,124</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,065,973,183</t>
+          <t>4,978,818,559</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-74,370,446</t>
+          <t>-56,886,455</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
